--- a/data/argentina/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -548,109 +548,129 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1561765420134601</v>
+        <v>1.201488126464561</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2239759832398515</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0.004432033590611902</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.5721272302628648</v>
+      </c>
       <c r="G2" t="n">
-        <v>0.07822811398041717</v>
+        <v>0.3075257307041065</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07732787161434235</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>-0.5382567203898148</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.08007185059073</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.95803841990848</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7409859536721733</v>
+        <v>-0.6992003961930476</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.8326118385310204</v>
+        <v>-1.409233378731123</v>
       </c>
       <c r="P2" t="n">
-        <v>1.166878927577926</v>
+        <v>-0.8293735702701835</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.02284952047622028</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0.8111766312268068</v>
+        <v>-0.7093821835878403</v>
       </c>
       <c r="T2" t="n">
-        <v>1.297500932775118</v>
+        <v>-0.8122013573169848</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5573278993376168</v>
+        <v>-0.9652035122370143</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9001793689788737</v>
+        <v>-0.697561835777998</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ngdGLTFj</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.108287446308644</v>
+        <v>-0.4328271057809235</v>
       </c>
       <c r="C3" t="n">
-        <v>1.895897477339437</v>
+        <v>-0.5274546814648047</v>
       </c>
       <c r="D3" t="n">
-        <v>1.540904293584067</v>
+        <v>1.201488126464561</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2328400504210754</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>1.831696168234319</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.2986900890986556</v>
+      </c>
       <c r="G3" t="n">
-        <v>0.07822811398041717</v>
+        <v>1.08713762756465</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.07732787161434235</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>-0.9991855691652871</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.400246238322442</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7579535432858534</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9436107882356528</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.00389729413922996</v>
+      </c>
       <c r="M3" t="n">
-        <v>-0.02559696060356714</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>-0.3946324432398603</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.03064901658274093</v>
+      </c>
       <c r="O3" t="n">
-        <v>-0.07387075559555495</v>
+        <v>0.1613412950830007</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0652726515804892</v>
+        <v>0.03891176263810506</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.02284952047622028</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0.07168278675885886</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.03732676197547548</v>
+      </c>
       <c r="S3" t="n">
-        <v>0.2068024694600285</v>
+        <v>0.3245703269545217</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1795598615351676</v>
+        <v>-0.538861393851861</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2269176010063478</v>
+        <v>0.1559988636318544</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1456733251835179</v>
+        <v>-0.09505645621124671</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -660,49 +680,67 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8350088762524709</v>
+        <v>-0.4955927091329655</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2328400504210754</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>-1.822832101053095</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.05508245424326898</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.526855203085408</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.074994250324339</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7325189079763328</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.8421596255443148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.5546969904329964</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.00389729413922996</v>
+      </c>
       <c r="M4" t="n">
-        <v>0.1781087095362066</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>-0.6865791026913443</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.003262809793276085</v>
+      </c>
       <c r="O4" t="n">
-        <v>-0.2010763038816309</v>
+        <v>-0.6775441312277146</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4605563619693762</v>
+        <v>-0.5067322321598766</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.02284952047622028</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>-0.005612131645608215</v>
+      </c>
       <c r="S4" t="n">
-        <v>-0.04989454760838542</v>
+        <v>-0.4108215211664284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1930878370263619</v>
+        <v>-0.6438547859621697</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.538757378974223</v>
+        <v>0.2939836417440193</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09214190878493779</v>
+        <v>-0.7268339015992392</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -712,49 +750,67 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1832396251060453</v>
+        <v>0.5226557922255507</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.051240117883559</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>0.6896560840820022</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09903666168564863</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.1510695027432722</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.3077922960020786</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.6576928624812545</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.7088168614751341</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9436107882356528</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.991517305146509</v>
+      </c>
       <c r="M5" t="n">
-        <v>-0.7242312430767933</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>-0.1268479206461148</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1.913450733358449</v>
+      </c>
       <c r="O5" t="n">
-        <v>-0.4696333699082302</v>
+        <v>0.2197475359821119</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4318852430369984</v>
+        <v>0.2779396394305501</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.02284952047622028</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>-0.5562934401005762</v>
+      </c>
       <c r="S5" t="n">
-        <v>-0.449244664172065</v>
+        <v>0.2742856264005784</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9166693758933337</v>
+        <v>-0.4583168040062283</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05863185964999865</v>
+        <v>-0.1821126465017528</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5498506471674175</v>
+        <v>0.07011176330925011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -763,36 +819,68 @@
       <c r="C6" t="n">
         <v>-0.5274546814648047</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-0.1561765420134601</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6896560840820022</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.392438653755492</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3533852540488444</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.07732787161434235</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1146470099951829</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.9755023896134956</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2881011350681189</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.4949563556822049</v>
+      </c>
       <c r="M6" t="n">
-        <v>-0.4703829976630099</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+        <v>-0.07462100576288724</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.5578334972799391</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.5518052604950172</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.1433076472388063</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.02284952047622028</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.700450850690882</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.1409962970569636</v>
+      </c>
       <c r="T6" t="n">
-        <v>-0.7013301120200316</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>-0.0470280175574958</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.3912252345233541</v>
+      </c>
       <c r="V6" t="n">
-        <v>0.2733460863791546</v>
+        <v>-0.07888694996544537</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -802,55 +890,65 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D7" t="n">
-        <v>1.201488126464561</v>
+        <v>0.5226557922255507</v>
       </c>
       <c r="E7" t="n">
-        <v>1.603288151403856</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>0.9180641009124656</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-2.013886701855968</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.1510695027432722</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3836009771611301</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8226252264319172</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.824695655839299</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-0.4949563556822049</v>
+        <v>1.0016045937821</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9193646425676369</v>
+        <v>2.296336807553564</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.455135221819446</v>
+        <v>1.016873393114289</v>
       </c>
       <c r="O7" t="n">
-        <v>1.055647710303701</v>
+        <v>1.157106381325789</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2585827453420804</v>
+        <v>1.204194689802699</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.02284952047622028</v>
+        <v>0.3813729362401343</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1180549119060467</v>
+        <v>0.9890740014275015</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5886903563177479</v>
+        <v>1.538918400544946</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6906742992017448</v>
+        <v>1.060182043914796</v>
       </c>
       <c r="U7" t="n">
-        <v>1.504681507944074</v>
+        <v>0.101572589912511</v>
       </c>
       <c r="V7" t="n">
-        <v>1.303444898515224</v>
+        <v>1.109597160888055</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -859,48 +957,54 @@
       <c r="C8" t="n">
         <v>-0.5274546814648047</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.1832396251060453</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.2328400504210754</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>1.391648601734637</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3075257307041065</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1531365527733938</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.5289695504018482</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.308788569267592</v>
+      </c>
       <c r="K8" t="n">
-        <v>-0.5546969904329964</v>
+        <v>0.1944568989013283</v>
       </c>
       <c r="L8" t="n">
         <v>0.00389729413922996</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2893722785246032</v>
+        <v>-1.537971901916906</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01043029360145634</v>
+        <v>-0.03749556828010714</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-0.04309305839908771</v>
+        <v>-0.1786010243539751</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>0.137115340433376</v>
+        <v>-1.350599101955916</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.185603923318278</v>
+        <v>-1.081529936519022</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -910,57 +1014,67 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1561765420134601</v>
+        <v>0.862071959345056</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9180641009124656</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>1.831696168234319</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.5969851521868837</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3075257307041065</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1531365527733938</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1146470099951829</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.04210304112923063</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.7563223159020717</v>
+        <v>1.833231031820163</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00389729413922996</v>
+        <v>1.500458243603535</v>
       </c>
       <c r="M9" t="n">
-        <v>1.611352505102022</v>
+        <v>0.6195256191727053</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01043029360145634</v>
+        <v>1.496132011929924</v>
       </c>
       <c r="O9" t="n">
-        <v>1.806317079276125</v>
+        <v>0.2363943958364532</v>
       </c>
       <c r="P9" t="n">
-        <v>1.393562407629544</v>
+        <v>0.3364064143789772</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.028116988334245</v>
+        <v>-0.435321415084745</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1702599092745648</v>
+        <v>0.7843704783892672</v>
       </c>
       <c r="S9" t="n">
-        <v>1.304372927366101</v>
+        <v>0.2235111569699989</v>
       </c>
       <c r="T9" t="n">
-        <v>1.311421258056607</v>
+        <v>0.4178366102584586</v>
       </c>
       <c r="U9" t="n">
-        <v>1.458843449253028</v>
+        <v>-0.08455136068661402</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33851777446255</v>
+        <v>0.7181239327335417</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -970,55 +1084,67 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8350088762524709</v>
+        <v>-0.1561765420134601</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6807920169007784</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>0.6896560840820022</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.5273829707996303</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.114119492982767</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7984369410590552</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2819873156984111</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.09123972293995006</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6938928251242115</v>
+      </c>
       <c r="L10" t="n">
-        <v>0.5027509439606648</v>
+        <v>1.0016045937821</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4108111145283109</v>
+        <v>0.3555715936364534</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4623027056276263</v>
+        <v>1.10587856518005</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4833910883677959</v>
+        <v>0.5980005547814092</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1731124566571907</v>
+        <v>0.4925937477155677</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1752178696039955</v>
+        <v>-0.02284952047622028</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1097137968266364</v>
+        <v>0.9400604818267975</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1183959987905715</v>
+        <v>0.4003462405543869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8762465384391399</v>
+        <v>0.6352649267074142</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.036549779320985</v>
+        <v>0.4679618400403635</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9129956203455609</v>
+        <v>0.7922664804858794</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1028,55 +1154,67 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.513841210491482</v>
+        <v>1.201488126464561</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.822832101053095</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>1.603288151403856</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.07496879178248447</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.683311431046242</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.921043266716232</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.852411723067167</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6246107792166727</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.617849288636545</v>
+      </c>
       <c r="L11" t="n">
-        <v>-0.4949563556822049</v>
+        <v>-1.991517305146509</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.459577853774812</v>
+        <v>1.049490400570241</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5099076353983757</v>
+        <v>-2.00245590542421</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9917734613011174</v>
+        <v>1.112889768169742</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.238159858797131</v>
+        <v>0.5267056489979984</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3903804474632186</v>
+        <v>0.6628080505987708</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.6370215900311474</v>
+        <v>-0.4986304758644539</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.562708850000858</v>
+        <v>0.6701672062286861</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6549087204909053</v>
+        <v>0.9967203569882248</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2101687006592267</v>
+        <v>0.5392121158043387</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.05940461914697</v>
+        <v>1.157014736335656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1086,55 +1224,65 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1561765420134601</v>
+        <v>2.219736627823077</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.594424084222632</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>3.2021442692171</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.815023326463816</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5368233474277958</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.3077922960020786</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.08007185059073</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6246107792166727</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-0.4949563556822049</v>
+        <v>1.0016045937821</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8544340332882727</v>
+        <v>-0.08751732745444216</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5030610837010094</v>
+        <v>1.023719944811656</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9610968907092107</v>
+        <v>-0.4117958266642582</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7373672313237424</v>
+        <v>-0.1584414943392534</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.6323229169873229</v>
+        <v>0.1724945168670813</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.3371741760033114</v>
+        <v>0.8160851087191345</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6463739500317605</v>
+        <v>-0.03808982402668282</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6264697360669089</v>
+        <v>-0.5608042047875267</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0118924458316151</v>
+        <v>-0.3720702719981028</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.914911566415749</v>
+        <v>0.1243693128201564</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1144,57 +1292,65 @@
         <v>-0.5274546814648047</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.550338213208514</v>
+        <v>-0.1561765420134601</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.594424084222632</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>-0.8668444443222985</v>
-      </c>
+        <v>0.004432033590611902</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1984683493817247</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.1510695027432722</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3836009771611301</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.2071612702033326</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.242187917751857</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-0.9938100055036397</v>
+        <v>0.5027509439606648</v>
       </c>
       <c r="M13" t="n">
-        <v>0.337843754538362</v>
+        <v>-0.8464263342720058</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.037092116095574</v>
+        <v>0.4965354641144573</v>
       </c>
       <c r="O13" t="n">
-        <v>0.363013862945152</v>
+        <v>-0.9350544365721504</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2641596299888816</v>
+        <v>-0.6863231999699155</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9884541716567059</v>
+        <v>-0.02284952047622028</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.6485541828783719</v>
+        <v>0.1125969450384425</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2780687652250888</v>
+        <v>-0.5687893658472352</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3815189409515502</v>
+        <v>-0.9024310155496974</v>
       </c>
       <c r="U13" t="n">
-        <v>1.481761233202183</v>
+        <v>-0.5186449940417578</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1362331306546752</v>
+        <v>-0.8375287683672984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1203,230 +1359,46 @@
       <c r="C14" t="n">
         <v>-0.5274546814648047</v>
       </c>
-      <c r="D14" t="n">
-        <v>-0.4955927091329655</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.6807920169007784</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.5713371782420099</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.1510695027432722</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3836009771611301</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.7864161745606607</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.308788569267592</v>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-0.4949563556822049</v>
+        <v>-2.989224604789379</v>
       </c>
       <c r="M14" t="n">
-        <v>1.090940575635338</v>
+        <v>-1.11151757528674</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.455135221819446</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.5692047787036034</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.6463452774771209</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.02284952047622028</v>
-      </c>
+        <v>-3.036285211726507</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>-0.0603919476699244</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3128450601477537</v>
-      </c>
+        <v>-1.533680683902849</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
-        <v>1.429218082707353</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.2890152428249995</v>
-      </c>
+        <v>-1.503886222367548</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.8129131568815668</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>nkx6zI2q</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.4328271057809235</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.5274546814648047</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.1561765420134601</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.6807920169007784</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>-0.9917034258780189</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.0016045937821</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.1429779085246948</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.044259599903754</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.4320296759270247</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.07238516278043777</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.02284952047622028</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.5623680660801964</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.05631384414812571</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.05417267699332151</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.9635933180238372</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.07974857337874366</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>pdWqnF1e</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.4328271057809235</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.5274546814648047</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.1561765420134601</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4612480672515388</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>-0.3674085180994152</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.4949563556822049</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2681853882633313</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.4072093599378825</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.4172993541482352</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.6254974883107738</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.02284952047622028</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-0.3544730652741481</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.298728632852053</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.3428408847345717</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.2473022487446255</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5969663416692551</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>noM4eJv9</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.4328271057809235</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.5274546814648047</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.540904293584067</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.2239759832398515</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>-0.9292739351001587</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.00389729413922996</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-0.01590394537618543</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.02412339699618876</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-0.8173414769233308</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-0.3781015817206864</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-0.1748221076582097</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-0.1555358386595262</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.4547602096317814</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.1456378322595639</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-1.078102180033233</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.6564273139735144</v>
+        <v>-0.8643038839251529</v>
       </c>
     </row>
   </sheetData>
